--- a/questionnaire_templates/047_parenting_strategies_implementation_guide--questionnaire_templates.xlsx
+++ b/questionnaire_templates/047_parenting_strategies_implementation_guide--questionnaire_templates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -538,7 +538,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is the child's age?</t>
+          <t>What Is The Childs Age</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Parent Goals And Expectations Other</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Careprovider Goals And Expectations Other</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Implementation Plan Other</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Progress Tracking Other</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Reflection Other</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Parent Child Interaction Other</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Parent Child Interaction Frequency Other</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>parent_child_interaction_frequency_other</t>
+          <t>parent_child_interaction_frequency_other_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Parent Child Interaction Frequency Other 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
